--- a/用卷/2007.xlsx
+++ b/用卷/2007.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E08F496-64A8-4A15-9A1F-C3E19A3E662A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC9E5A0-1F50-4D84-A671-00CA98D0893A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="82">
   <si>
     <t>年份</t>
   </si>
@@ -950,9 +950,7 @@
       <c r="C11" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>48</v>
-      </c>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
@@ -962,7 +960,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D12" s="1"/>
     </row>
@@ -1146,9 +1144,7 @@
       <c r="C27" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="D27" s="1"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1">

--- a/用卷/2007.xlsx
+++ b/用卷/2007.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC9E5A0-1F50-4D84-A671-00CA98D0893A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6345382A-51DB-4708-814E-BE9D37ECF441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -966,7 +966,7 @@
     </row>
     <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
